--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -777,7 +777,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Jupyter notebook exercise: ODEs in Python</t>
+          <t>Jupyter notebook exercise: ODEs in Python [BRING LAPTOP]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ODEs: 1.33</t>
+          <t>ODEs: 1.33, 1.36 (if you don't have experience with computational tools, feel free to completely skip this)</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Redo the class notebook's exercises from scratch in a fresh notebook on jupyterhub.smith.edu. Sec 1.2: 1.36 (compound interest, by computer; moved here from WHW01)</t>
+          <t>Redo the class notebook's exercises from scratch in a fresh notebook on jupyterhub.smith.edu. Sec 1.2: 1.36 (compound interest, by computer; it was optional Depth on WHW01 before we had Python, so here it is with the tools)</t>
         </is>
       </c>
     </row>

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3.1-3.4</t>
+          <t>3.1-3.3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.4-3.5</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Vector and scalar fields; the gradient</t>
+          <t>Vector and scalar fields; potential</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8.1-8.4</t>
+          <t>8.1-8.3</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Work, path integrals, and the gradient theorem</t>
+          <t>The gradient; work, path integrals, and the gradient theorem</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4-8.5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -717,14 +717,10 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Methods of solving ODEs: guess and check</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
+          <t>Mountain Day (no class)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>10.1, 10.3</t>
@@ -931,11 +927,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Flex day (snow / Mountain Day buffer)</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>Linear approximations</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2.1-2.2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>DE 2.2.1 Parts 1-5</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>WHW05</t>
@@ -1017,17 +1021,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Linear approximations</t>
+          <t>Maclaurin series</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2.1-2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>DE 2.2.1 Parts 1-5</t>
+          <t>DE 2.3.1 Parts 1-3</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
@@ -1047,17 +1051,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Maclaurin series</t>
+          <t>Taylor series; finding one series from another</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4-2.5 (convergence: App. C)</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>DE 2.3.1 Parts 1-3</t>
+          <t>2.209</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1081,17 +1085,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Taylor series; finding one series from another</t>
+          <t>Properties of matrices</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2.4-2.5 (convergence: App. C)</t>
+          <t>6.1-6.2</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2.209</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1111,17 +1115,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Properties of matrices</t>
+          <t>Matrix x column; vector transformations</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6.1-6.2</t>
+          <t>6.3-6.4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>DE 6.3.1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1171,17 +1175,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Matrix x column; vector transformations</t>
+          <t>Matrix multiplication; identity and inverse</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6.3-6.4</t>
+          <t>6.5-6.6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>DE 6.3.1</t>
+          <t>DE 6.5.1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1205,17 +1209,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Matrix multiplication; identity, determinant, inverse</t>
+          <t>Determinants; finding eigenvalues and eigenvectors</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6.5-6.7</t>
+          <t>6.7-6.8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>DE 6.5.1</t>
+          <t>DE 6.8.1 Parts 1-3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1235,17 +1239,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Finding eigenvalues and eigenvectors</t>
+          <t>Eigenvectors; the two-coupled-oscillator problem</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.8-6.9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>DE 6.8.1 Parts 1-3</t>
+          <t>6.166</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1269,17 +1273,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Eigenvalues and eigenvectors, continued</t>
+          <t>Setting up 1D and 2D integrals</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>5.1-5.2</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6.166</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1299,17 +1303,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>The two-coupled-oscillator problem</t>
+          <t>Cartesian 2D integrals</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>5.3-5.4</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6.175</t>
+          <t>DE 5.4.1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1329,19 +1333,15 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Setting up 1D and 2D integrals</t>
+          <t>Polar coordinates</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5.1-5.2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>WHW09</t>
@@ -1363,17 +1363,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Cartesian 2D integrals; polar coordinates</t>
+          <t>Line integrals and surface integrals</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5.3-5.4, 5.6</t>
+          <t>5.8, 5.10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>DE 5.4.1</t>
+          <t>5.163 parts a and d</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1393,17 +1393,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Line integrals and surface integrals</t>
+          <t>Cylindrical and spherical coordinates</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5.8, 5.10</t>
+          <t>5.5, 5.7; App. D</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5.163 parts a and d</t>
+          <t>DE 5.7.1 Parts 1-4</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1423,17 +1423,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Coordinate systems: cylindrical and spherical (review + practice)</t>
+          <t>Vector and scalar fields; potential</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5.5, 5.7; App. D</t>
+          <t>8.1-8.3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>DE 5.7.1 Parts 1-4</t>
+          <t>DE 8.2.1 Parts 5-6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Vector and scalar fields; potential</t>
+          <t>The gradient; equipotentials</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8.1-8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>DE 8.2.1 Parts 5-6</t>
+          <t>DE 8.4.1</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1487,17 +1487,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>The gradient; work, path integrals, and the gradient theorem</t>
+          <t>Potential from a field; the gradient theorem; divergence and curl (Feynman)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8.4-8.5</t>
+          <t>8.5-8.6; Feynman Vol II Ch 3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>DE 8.4.1</t>
+          <t>Read Feynman II Ch 3 sections 3-1 to 3-6; in one or two sentences, what does the flux of a vector field out of a tiny box measure, and what does the circulation around a tiny loop measure?</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1547,17 +1547,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Divergence and curl, geometrically</t>
+          <t>Divergence, curl, and the Laplacian; the divergence theorem</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Feynman Vol II Ch 2-3</t>
+          <t>8.6-8.7, 8.9; Feynman Vol II Ch 2</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Read Feynman II Ch 3 sections 3-1 to 3-6; in one or two sentences, what does the flux of a vector field out of a tiny box measure, and what does the circulation around a tiny loop measure?</t>
+          <t>DE 8.6.1 Parts 1-9</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1613,17 +1613,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Divergence, curl, and the Laplacian</t>
+          <t>Divergence theorem; Stokes' theorem</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8.6-8.7</t>
+          <t>8.9-8.10</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>DE 8.6.1 Parts 1-9</t>
+          <t>DE 8.9.1</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Divergence theorem; Stokes' theorem</t>
+          <t>Conservative vector fields</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>8.9-8.10; Feynman Vol II Ch 3</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>DE 8.9.1</t>
+          <t>DE 8.11.1 Parts 1-2, 4-5, 7-8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1673,17 +1673,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Conservative vector fields</t>
+          <t>Introduction to Fourier series</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.1-9.3</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>DE 8.11.1 Parts 1-2, 4-5, 7-8</t>
+          <t>DE 9.2.1 Parts 1-3</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Introduction to Fourier series</t>
+          <t>Fourier series: different periods, finite domains</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9.1-9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>DE 9.2.1 Parts 1-3</t>
+          <t>DE 9.4.1 Part 1</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1737,19 +1737,15 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Fourier series: different periods, finite domains, complex exponentials</t>
+          <t>Fourier series with complex exponentials</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9.4-9.5</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>DE 9.4.1 Part 1</t>
-        </is>
-      </c>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
     </row>

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -45,12 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -704,56 +704,48 @@
       <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Wed Sep 23</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Mountain Day!!</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Wed Sep 23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Mountain Day (no class)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10.1, 10.3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Fri Sep 25</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Quiz 1 (Ch 1)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>WHW03</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Quiz 1 (Ch 1)</t>
         </is>
@@ -764,7 +756,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -794,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
@@ -824,7 +816,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
@@ -858,7 +850,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
@@ -888,7 +880,7 @@
         <v>5</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -918,7 +910,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
@@ -948,22 +940,22 @@
       <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Mon Oct 12</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>No class - Autumn recess</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1012,7 +1004,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
@@ -1042,7 +1034,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
@@ -1076,7 +1068,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
@@ -1106,7 +1098,7 @@
         <v>7</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
@@ -1132,30 +1124,30 @@
       <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Fri Oct 23</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Quiz 2 (Ch 10, 3, 2)</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>WHW07</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Quiz 2 (Ch 10, 3, 2)</t>
         </is>
@@ -1166,7 +1158,7 @@
         <v>8</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
@@ -1200,7 +1192,7 @@
         <v>8</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
@@ -1230,7 +1222,7 @@
         <v>8</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
@@ -1264,7 +1256,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
@@ -1294,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
@@ -1324,7 +1316,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
@@ -1354,7 +1346,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
@@ -1384,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
@@ -1414,7 +1406,7 @@
         <v>10</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -1448,7 +1440,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -1478,7 +1470,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -1504,30 +1496,30 @@
       <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Fri Nov 20</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Quiz 3 (Ch 6, 5)</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>WHW11</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Quiz 3 (Ch 6, 5)</t>
         </is>
@@ -1538,7 +1530,7 @@
         <v>12</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
@@ -1564,47 +1556,47 @@
       <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="A36" s="3" t="n"/>
+      <c r="B36" s="3" t="n"/>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Wed Nov 25</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>No class - Thanksgiving</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="A37" s="3" t="n"/>
+      <c r="B37" s="3" t="n"/>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Fri Nov 27</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>No class - Thanksgiving</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr"/>
-      <c r="G37" s="4" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
@@ -1634,7 +1626,7 @@
         <v>13</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
@@ -1664,7 +1656,7 @@
         <v>13</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
@@ -1698,7 +1690,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
@@ -1728,7 +1720,7 @@
         <v>14</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
@@ -1754,7 +1746,7 @@
         <v>14</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
@@ -1788,7 +1780,7 @@
         <v>15</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
@@ -1814,22 +1806,22 @@
       <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Sat Dec 19</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Final exam period Dec 19-22 (registrar schedules)</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Final (Ch 8, 9, 11 + redemptions)</t>
         </is>

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Sec 10.11: 10.252, 10.261, 10.263, 10.264. Complex numbers: 3.49, 3.54. Euler / complex ODE: 3.92, 3.94, 3.95</t>
+          <t>Sec 10.11: 10.252, 10.261, 10.263, 10.264 (optional). Complex numbers: 3.49, 3.54. Euler / complex ODE: 3.92, 3.94, 3.95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -919,7 +919,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Linear approximations</t>
+          <t>Linear approximations; the Maclaurin machine</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Maclaurin series</t>
+          <t>Maclaurin series in Python; Taylor series; series from a series [BRING LAPTOP]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.3-2.5</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>DE 2.3.1 Parts 1-3</t>
+          <t>2.30 (a)-(e)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Maclaurin series in Python; Taylor series; series from a series [BRING LAPTOP]</t>
+          <t>Series day 2: back to the crystal, Taylor series, SymPy [BRING LAPTOP]</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -1043,17 +1043,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Taylor series; finding one series from another</t>
+          <t>Properties of matrices</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2.4-2.5 (convergence: App. C)</t>
+          <t>6.1-6.2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2.209</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1077,17 +1077,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Properties of matrices</t>
+          <t>Matrix x column; vector transformations</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6.1-6.2</t>
+          <t>6.3-6.4</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>DE 6.3.1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Matrix x column; vector transformations</t>
+          <t>Matrix multiplication; identity and inverse</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6.3-6.4</t>
+          <t>6.5-6.6</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>DE 6.3.1</t>
+          <t>DE 6.5.1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1167,17 +1167,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Matrix multiplication; identity and inverse</t>
+          <t>Determinants; finding eigenvalues and eigenvectors</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6.5-6.6</t>
+          <t>6.7-6.8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>DE 6.5.1</t>
+          <t>DE 6.8.1 Parts 1-3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Determinants; finding eigenvalues and eigenvectors</t>
+          <t>Eigenvectors; the two-coupled-oscillator problem</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6.7-6.8</t>
+          <t>6.8-6.9</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>DE 6.8.1 Parts 1-3</t>
+          <t>6.166</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1231,17 +1231,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Eigenvectors; the two-coupled-oscillator problem</t>
+          <t>Setting up 1D and 2D integrals</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6.8-6.9</t>
+          <t>5.1-5.2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6.166</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Setting up 1D and 2D integrals</t>
+          <t>Cartesian 2D integrals</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5.1-5.2</t>
+          <t>5.3-5.4</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>DE 5.4.1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1295,19 +1295,15 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Cartesian 2D integrals</t>
+          <t>Polar coordinates</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5.3-5.4</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>DE 5.4.1</t>
-        </is>
-      </c>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
@@ -1325,15 +1321,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Polar coordinates</t>
+          <t>Line integrals and surface integrals</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>5.8, 5.10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5.163 parts a and d</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>WHW09</t>
@@ -1355,17 +1355,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Line integrals and surface integrals</t>
+          <t>Cylindrical and spherical coordinates</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5.8, 5.10</t>
+          <t>5.5, 5.7; App. D</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5.163 parts a and d</t>
+          <t>DE 5.7.1 Parts 1-4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Cylindrical and spherical coordinates</t>
+          <t>Vector and scalar fields; potential</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5.5, 5.7; App. D</t>
+          <t>8.1-8.3</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>DE 5.7.1 Parts 1-4</t>
+          <t>DE 8.2.1 Parts 5-6</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1415,17 +1415,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Vector and scalar fields; potential</t>
+          <t>The gradient; equipotentials</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8.1-8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>DE 8.2.1 Parts 5-6</t>
+          <t>DE 8.4.1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>The gradient; equipotentials</t>
+          <t>Potential from a field; the gradient theorem; divergence and curl (Feynman)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.5-8.6; Feynman Vol II Ch 3</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>DE 8.4.1</t>
+          <t>Read Feynman II Ch 3 sections 3-1 to 3-6; in one or two sentences, what does the flux of a vector field out of a tiny box measure, and what does the circulation around a tiny loop measure?</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1479,17 +1479,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Potential from a field; the gradient theorem; divergence and curl (Feynman)</t>
+          <t>Divergence, curl, and the Laplacian; the divergence theorem</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8.5-8.6; Feynman Vol II Ch 3</t>
+          <t>8.6-8.7, 8.9; Feynman Vol II Ch 2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Read Feynman II Ch 3 sections 3-1 to 3-6; in one or two sentences, what does the flux of a vector field out of a tiny box measure, and what does the circulation around a tiny loop measure?</t>
+          <t>DE 8.6.1 Parts 1-9</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1539,17 +1539,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Divergence, curl, and the Laplacian; the divergence theorem</t>
+          <t>Divergence theorem; Stokes' theorem</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8.6-8.7, 8.9; Feynman Vol II Ch 2</t>
+          <t>8.9-8.10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>DE 8.6.1 Parts 1-9</t>
+          <t>DE 8.9.1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Divergence theorem; Stokes' theorem</t>
+          <t>Conservative vector fields</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8.9-8.10</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>DE 8.9.1</t>
+          <t>DE 8.11.1 Parts 1-2, 4-5, 7-8</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1635,17 +1635,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Conservative vector fields</t>
+          <t>Introduction to Fourier series</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.1-9.3</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>DE 8.11.1 Parts 1-2, 4-5, 7-8</t>
+          <t>DE 9.2.1 Parts 1-3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1665,17 +1665,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Introduction to Fourier series</t>
+          <t>Fourier series: different periods, finite domains</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9.1-9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>DE 9.2.1 Parts 1-3</t>
+          <t>DE 9.4.1 Part 1</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1699,19 +1699,15 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Fourier series: different periods, finite domains</t>
+          <t>Fourier series with complex exponentials</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>DE 9.4.1 Part 1</t>
-        </is>
-      </c>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
@@ -1729,15 +1725,19 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Fourier series with complex exponentials</t>
+          <t>Intro to PDEs: the heat equation; separation of variables</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr"/>
+          <t>11.1-11.2, 11.4</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>DE 11.2.1 Parts 1-2</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
     </row>
@@ -1755,17 +1755,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Intro to PDEs: the heat equation; separation of variables</t>
+          <t>Normal modes of the wave equation; Fourier transforms</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11.1-11.2, 11.4</t>
+          <t>11.3, 9.6</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>DE 11.2.1 Parts 1-2</t>
+          <t>DE 11.3.1 Part 1</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -1789,19 +1789,11 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Normal modes of the wave equation; Fourier transforms</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>11.3, 9.6</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>DE 11.3.1 Part 1</t>
-        </is>
-      </c>
+          <t>Flex (freed when 2026-10-14 got a day ahead: a day ahead: Michael's two-day series plan put Taylor, the SymPy notebook and the crystal on Wed Oct 14 (class 14); Friday's content was covered (decided 2026-10-12 on the assumption that Wednesday lands))</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
     </row>

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.2 (a)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1180,11 +1180,7 @@
           <t>DE 6.8.1 Parts 1-3</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Non-Newtonian Scientist due</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -1214,7 +1210,11 @@
           <t>6.166</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Non-Newtonian Scientist due</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Flex (freed when 2026-10-14 got a day ahead: a day ahead: Michael's two-day series plan put Taylor, the SymPy notebook and the crystal on Wed Oct 14 (class 14); Friday's content was covered (decided 2026-10-12 on the assumption that Wednesday lands))</t>
+          <t>Flex day</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -1167,19 +1167,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Determinants; finding eigenvalues and eigenvectors</t>
+          <t>Matrix multiplication; identity and inverse (continued)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6.7-6.8</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>DE 6.8.1 Parts 1-3</t>
-        </is>
-      </c>
+          <t>6.5-6.6</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
@@ -1197,17 +1193,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Eigenvectors; the two-coupled-oscillator problem</t>
+          <t>Determinants; finding eigenvalues and eigenvectors</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6.8-6.9</t>
+          <t>6.7-6.8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6.166</t>
+          <t>DE 6.8.1 Parts 1-3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1231,17 +1227,17 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Setting up 1D and 2D integrals</t>
+          <t>Eigenvectors; the two-coupled-oscillator problem</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5.1-5.2</t>
+          <t>6.8-6.9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>6.166</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1265,17 +1261,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Cartesian 2D integrals</t>
+          <t>Setting up 1D and 2D integrals</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5.3-5.4</t>
+          <t>5.1-5.2</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>DE 5.4.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1295,15 +1291,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Polar coordinates</t>
+          <t>Cartesian 2D integrals</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr"/>
+          <t>5.3-5.4</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>DE 5.4.1</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
@@ -1321,19 +1321,15 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Line integrals and surface integrals</t>
+          <t>Polar coordinates</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5.8, 5.10</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5.163 parts a and d</t>
-        </is>
-      </c>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>WHW09</t>
@@ -1355,17 +1351,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Cylindrical and spherical coordinates</t>
+          <t>Line integrals and surface integrals</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5.5, 5.7; App. D</t>
+          <t>5.8, 5.10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>DE 5.7.1 Parts 1-4</t>
+          <t>5.163 parts a and d</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1385,17 +1381,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Vector and scalar fields; potential</t>
+          <t>Cylindrical and spherical coordinates</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8.1-8.3</t>
+          <t>5.5, 5.7; App. D</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>DE 8.2.1 Parts 5-6</t>
+          <t>DE 5.7.1 Parts 1-4</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1415,17 +1411,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>The gradient; equipotentials</t>
+          <t>Vector and scalar fields; potential</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1-8.3</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>DE 8.4.1</t>
+          <t>DE 8.2.1 Parts 5-6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1449,17 +1445,17 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Potential from a field; the gradient theorem; divergence and curl (Feynman)</t>
+          <t>The gradient; equipotentials</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8.5-8.6; Feynman Vol II Ch 3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Read Feynman II Ch 3 sections 3-1 to 3-6; in one or two sentences, what does the flux of a vector field out of a tiny box measure, and what does the circulation around a tiny loop measure?</t>
+          <t>DE 8.4.1</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1479,17 +1475,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Divergence, curl, and the Laplacian; the divergence theorem</t>
+          <t>Potential from a field; the gradient theorem; divergence and curl (Feynman)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8.6-8.7, 8.9; Feynman Vol II Ch 2</t>
+          <t>8.5-8.6; Feynman Vol II Ch 3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>DE 8.6.1 Parts 1-9</t>
+          <t>Read Feynman II Ch 3 sections 3-1 to 3-6; in one or two sentences, what does the flux of a vector field out of a tiny box measure, and what does the circulation around a tiny loop measure?</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1539,17 +1535,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Divergence theorem; Stokes' theorem</t>
+          <t>Divergence, curl, and the Laplacian; the divergence theorem</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8.9-8.10</t>
+          <t>8.6-8.7, 8.9; Feynman Vol II Ch 2</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>DE 8.9.1</t>
+          <t>DE 8.6.1 Parts 1-9</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -1605,17 +1601,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Conservative vector fields</t>
+          <t>Divergence theorem; Stokes' theorem</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>8.9-8.10</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>DE 8.11.1 Parts 1-2, 4-5, 7-8</t>
+          <t>DE 8.9.1</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1635,17 +1631,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Introduction to Fourier series</t>
+          <t>Conservative vector fields</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9.1-9.3</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>DE 9.2.1 Parts 1-3</t>
+          <t>DE 8.11.1 Parts 1-2, 4-5, 7-8</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1665,17 +1661,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Fourier series: different periods, finite domains</t>
+          <t>Introduction to Fourier series</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1-9.3</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>DE 9.4.1 Part 1</t>
+          <t>DE 9.2.1 Parts 1-3</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1699,15 +1695,19 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Fourier series with complex exponentials</t>
+          <t>Fourier series: different periods, finite domains</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr"/>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>DE 9.4.1 Part 1</t>
+        </is>
+      </c>
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
@@ -1725,19 +1725,15 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Intro to PDEs: the heat equation; separation of variables</t>
+          <t>Fourier series with complex exponentials</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11.1-11.2, 11.4</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>DE 11.2.1 Parts 1-2</t>
-        </is>
-      </c>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
     </row>
@@ -1755,17 +1751,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Normal modes of the wave equation; Fourier transforms</t>
+          <t>Intro to PDEs: the heat equation; separation of variables</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11.3, 9.6</t>
+          <t>11.1-11.2, 11.4</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>DE 11.3.1 Part 1</t>
+          <t>DE 11.2.1 Parts 1-2</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -1789,11 +1785,19 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Flex day</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
+          <t>Normal modes of the wave equation; Fourier transforms</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>11.3, 9.6</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>DE 11.3.1 Part 1</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
     </row>

--- a/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
+++ b/SyllabusAndFirstDay/2026/PHY210 F2026 Calendar.xlsx
@@ -1261,19 +1261,15 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Setting up 1D and 2D integrals</t>
+          <t>Eigenvectors; the two-coupled-oscillator problem (continued)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5.1-5.2</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
+          <t>6.8-6.9</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
@@ -1291,17 +1287,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Cartesian 2D integrals</t>
+          <t>Setting up 1D and 2D integrals</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5.3-5.4</t>
+          <t>5.1-5.2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>DE 5.4.1</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1321,15 +1317,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Polar coordinates</t>
+          <t>Cartesian 2D integrals</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr"/>
+          <t>5.3-5.4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>DE 5.4.1</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>WHW09</t>
@@ -1351,17 +1351,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Line integrals and surface integrals</t>
+          <t>Polar, cylindrical and spherical coordinates</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5.8, 5.10</t>
+          <t>5.5-5.7; App. D</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5.163 parts a and d</t>
+          <t>DE 5.7.1 Parts 1-4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1381,17 +1381,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Cylindrical and spherical coordinates</t>
+          <t>Line integrals and surface integrals</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5.5, 5.7; App. D</t>
+          <t>5.8, 5.10</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>DE 5.7.1 Parts 1-4</t>
+          <t>5.163 parts a and d</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
